--- a/dr/includes/cities-sample.xlsx
+++ b/dr/includes/cities-sample.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>City</t>
   </si>
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.08984375" bestFit="1" customWidth="1"/>
@@ -408,7 +408,7 @@
     <col min="5" max="5" width="36.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -416,36 +416,48 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
